--- a/tables/adj_radio.xlsx
+++ b/tables/adj_radio.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="133" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="145" uniqueCount="98">
   <si>
     <t>Supplementary File Table Adjusted radiologic measurements in the whole cohort, by prior exposure</t>
   </si>
@@ -36,7 +36,7 @@
     <t>(0.028- 0.042)</t>
   </si>
   <si>
-    <t>[832]</t>
+    <t>[831]</t>
   </si>
   <si>
     <t>(0.035- 0.053)</t>
@@ -54,7 +54,7 @@
     <t>(0.028- 0.040)</t>
   </si>
   <si>
-    <t>[759]</t>
+    <t>[758]</t>
   </si>
   <si>
     <t>(0.030- 0.046)</t>
@@ -69,7 +69,7 @@
     <t>(0.017- 0.026)</t>
   </si>
   <si>
-    <t>[858]</t>
+    <t>[857]</t>
   </si>
   <si>
     <t>(0.020- 0.033)</t>
@@ -84,28 +84,43 @@
     <t>(0.016- 0.032)</t>
   </si>
   <si>
-    <t>[687]</t>
+    <t>[686]</t>
   </si>
   <si>
     <t>(0.024- 0.040)</t>
   </si>
   <si>
+    <t xml:space="preserve">  adj_wt_pan_quant</t>
+  </si>
+  <si>
+    <t>[611]</t>
+  </si>
+  <si>
+    <t>(0.057- 0.092)</t>
+  </si>
+  <si>
+    <t>[733]</t>
+  </si>
+  <si>
+    <t>(0.061- 0.102)</t>
+  </si>
+  <si>
     <t>USS Square Root Transformed</t>
   </si>
   <si>
     <t>(1.364- 1.533)</t>
   </si>
   <si>
-    <t>[837]</t>
+    <t>[836]</t>
   </si>
   <si>
     <t>(1.334- 1.546)</t>
   </si>
   <si>
-    <t>p=0.214</t>
-  </si>
-  <si>
-    <t>[764]</t>
+    <t>p=0.203</t>
+  </si>
+  <si>
+    <t>[763]</t>
   </si>
   <si>
     <t>(1.208- 1.483)</t>
@@ -114,22 +129,34 @@
     <t>(1.034- 1.225)</t>
   </si>
   <si>
-    <t>[863]</t>
+    <t>[862]</t>
   </si>
   <si>
     <t>(1.015- 1.221)</t>
   </si>
   <si>
-    <t>p=0.081</t>
+    <t>p=0.076</t>
   </si>
   <si>
     <t>(1.034- 1.261)</t>
   </si>
   <si>
-    <t>[692]</t>
-  </si>
-  <si>
-    <t>(1.068- 1.310)</t>
+    <t>[691]</t>
+  </si>
+  <si>
+    <t>(1.068- 1.311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  adj_sqrt_pan_quant</t>
+  </si>
+  <si>
+    <t>(1.881- 2.335)</t>
+  </si>
+  <si>
+    <t>[738]</t>
+  </si>
+  <si>
+    <t>(1.690- 2.211)</t>
   </si>
   <si>
     <t>CT Adjusted by weight</t>
@@ -289,7 +316,167 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="461">
+  <fonts count="501">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2143,7 +2330,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="461">
+  <borders count="501">
     <border>
       <left/>
       <right/>
@@ -5200,6 +5387,286 @@
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
@@ -5375,7 +5842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="461">
+  <cellXfs count="501">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -5838,103 +6305,103 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="120" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="121" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="122" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="127" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="128" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="129" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="127" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="128" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="133" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="134" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="135" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="140" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="141" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -6182,183 +6649,183 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="202" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="203" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="204" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="206" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="207" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="208" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="213" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="214" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="215" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="226" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="227" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="228" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="233" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="234" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="235" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="212" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="213" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="214" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="219" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="220" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="221" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="232" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="233" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="234" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="239" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="240" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="241" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="246" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="247" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -6686,183 +7153,183 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="328" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="329" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="330" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="332" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="333" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="334" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="339" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="340" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="341" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="331" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="333" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="352" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="353" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="354" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="359" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="360" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="361" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="335" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="337" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="338" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="339" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="340" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="341" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="343" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="345" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="346" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="347" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="349" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="351" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="353" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="355" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="357" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="358" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="359" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="360" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="363" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="365" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="366" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="367" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="371" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="372" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="373" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -7118,102 +7585,262 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="436" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="438" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="439" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="440" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="445" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="446" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="447" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="440" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="441" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="442" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="443" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="450" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="451" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="452" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="453" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="455" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="456" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="457" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="458" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="459" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="460" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="465" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="466" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="467" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="480" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="481" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="482" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="483" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="490" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="491" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="492" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="493" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7226,7 +7853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7285,7 +7912,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="49">
-        <v>0.043239288032054901</v>
+        <v>0.043260186910629273</v>
       </c>
       <c r="G4" s="51" t="s">
         <v>8</v>
@@ -7311,7 +7938,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="69">
-        <v>0.037283949553966522</v>
+        <v>0.037278337404131889</v>
       </c>
       <c r="G5" s="71" t="s">
         <v>14</v>
@@ -7337,7 +7964,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="89">
-        <v>0.025455452501773834</v>
+        <v>0.025507247075438499</v>
       </c>
       <c r="G6" s="91" t="s">
         <v>19</v>
@@ -7363,7 +7990,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="109">
-        <v>0.032175924628973007</v>
+        <v>0.032186448574066162</v>
       </c>
       <c r="G7" s="111" t="s">
         <v>24</v>
@@ -7373,228 +8000,228 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="115"/>
-      <c r="H8" s="116"/>
+      <c r="A8" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="122">
+        <v>0.070406831800937653</v>
+      </c>
+      <c r="D8" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="126" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="129">
+        <v>0.079921156167984009</v>
+      </c>
+      <c r="G8" s="131" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="134" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="119" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="120"/>
+      <c r="A9" s="135"/>
+      <c r="H9" s="136"/>
     </row>
     <row r="10">
-      <c r="A10" s="123" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="125" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="128">
-        <v>1.4456832408905029</v>
-      </c>
-      <c r="D10" s="130" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="135">
-        <v>1.4387494325637817</v>
-      </c>
-      <c r="G10" s="137" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="140" t="s">
-        <v>29</v>
-      </c>
+      <c r="A10" s="139" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="140"/>
     </row>
     <row r="11">
       <c r="A11" s="143" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B11" s="145" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C11" s="148">
-        <v>1.4491376876831055</v>
+        <v>1.4456832408905029</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" s="155">
-        <v>1.3490737676620483</v>
+        <v>1.4387494325637817</v>
       </c>
       <c r="G11" s="157" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H11" s="160" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="163" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B12" s="165" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C12" s="168">
-        <v>1.1135529279708862</v>
+        <v>1.4491376876831055</v>
       </c>
       <c r="D12" s="170" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="172" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" s="175">
-        <v>1.1090536117553711</v>
+        <v>1.3490737676620483</v>
       </c>
       <c r="G12" s="177" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H12" s="180" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="183" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B13" s="185" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" s="188">
+        <v>1.1135529279708862</v>
+      </c>
+      <c r="D13" s="190" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="195">
         <v>1.1090536117553711</v>
       </c>
-      <c r="D13" s="190" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="192" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="195">
-        <v>1.1916375160217285</v>
-      </c>
       <c r="G13" s="197" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" s="200" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="201"/>
-      <c r="H14" s="202"/>
+      <c r="A14" s="203" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="205" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="208">
+        <v>1.1090536117553711</v>
+      </c>
+      <c r="D14" s="210" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="212" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="215">
+        <v>1.1916375160217285</v>
+      </c>
+      <c r="G14" s="217" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="220" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="205" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="206"/>
+      <c r="A15" s="223" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="225" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="228">
+        <v>2.0873188972473145</v>
+      </c>
+      <c r="D15" s="230" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="232" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="235">
+        <v>1.9495640397071838</v>
+      </c>
+      <c r="G15" s="237" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="240" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="209" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="211" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="214">
-        <v>0.040916532278060913</v>
-      </c>
-      <c r="D16" s="216" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="218" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="221">
-        <v>0.043463777750730515</v>
-      </c>
-      <c r="G16" s="223" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="226" t="s">
-        <v>45</v>
-      </c>
+      <c r="A16" s="241"/>
+      <c r="H16" s="242"/>
     </row>
     <row r="17">
-      <c r="A17" s="229" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="231" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="234">
-        <v>0.041580772027373314</v>
-      </c>
-      <c r="D17" s="236" t="s">
+      <c r="A17" s="245" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="238" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="241">
-        <v>0.047818183898925781</v>
-      </c>
-      <c r="G17" s="243" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="246" t="s">
-        <v>9</v>
-      </c>
+      <c r="H17" s="246"/>
     </row>
     <row r="18">
       <c r="A18" s="249" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="251" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="254">
+        <v>0.040916532278060913</v>
+      </c>
+      <c r="D18" s="256" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="251" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="254">
-        <v>0.0322718545794487</v>
-      </c>
-      <c r="D18" s="256" t="s">
+      <c r="E18" s="258" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="258" t="s">
-        <v>43</v>
-      </c>
       <c r="F18" s="261">
-        <v>0.036572437733411789</v>
+        <v>0.043463777750730515</v>
       </c>
       <c r="G18" s="263" t="s">
         <v>53</v>
       </c>
       <c r="H18" s="266" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="269" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="271" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C19" s="274">
-        <v>0.027247956022620201</v>
+        <v>0.041580772027373314</v>
       </c>
       <c r="D19" s="276" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" s="278" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" s="281">
-        <v>0.031756754964590073</v>
+        <v>0.047818183898925781</v>
       </c>
       <c r="G19" s="283" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H19" s="286" t="s">
         <v>9</v>
@@ -7602,28 +8229,28 @@
     </row>
     <row r="20">
       <c r="A20" s="289" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B20" s="291" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="294">
-        <v>0.16771791875362396</v>
+        <v>0.0322718545794487</v>
       </c>
       <c r="D20" s="296" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E20" s="298" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F20" s="301">
-        <v>0.17431331425905228</v>
+        <v>0.036572437733411789</v>
       </c>
       <c r="G20" s="303" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="306" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -7631,201 +8258,253 @@
         <v>63</v>
       </c>
       <c r="B21" s="311" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="314">
+        <v>0.027247956022620201</v>
+      </c>
+      <c r="D21" s="316" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="314">
-        <v>1.035781741142273</v>
-      </c>
-      <c r="D21" s="316" t="s">
+      <c r="E21" s="318" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="321">
+        <v>0.031756754964590073</v>
+      </c>
+      <c r="G21" s="323" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="318" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="321">
-        <v>1.07194983959198</v>
-      </c>
-      <c r="G21" s="323" t="s">
-        <v>67</v>
-      </c>
       <c r="H21" s="326" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="327"/>
-      <c r="H22" s="328"/>
+      <c r="A22" s="329" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="331" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="334">
+        <v>0.16771791875362396</v>
+      </c>
+      <c r="D22" s="336" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="338" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="341">
+        <v>0.17431331425905228</v>
+      </c>
+      <c r="G22" s="343" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="346" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="331" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="332"/>
+      <c r="A23" s="349" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="351" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="354">
+        <v>1.035781741142273</v>
+      </c>
+      <c r="D23" s="356" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="358" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="361">
+        <v>1.07194983959198</v>
+      </c>
+      <c r="G23" s="363" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="366" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="335" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="337" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="340">
-        <v>1.6031218767166138</v>
-      </c>
-      <c r="D24" s="342" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="344" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="347">
-        <v>1.5620499849319458</v>
-      </c>
-      <c r="G24" s="349" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="352" t="s">
-        <v>72</v>
-      </c>
+      <c r="A24" s="367"/>
+      <c r="H24" s="368"/>
     </row>
     <row r="25">
-      <c r="A25" s="355" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="357" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="360">
-        <v>1.6124515533447266</v>
-      </c>
-      <c r="D25" s="362" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="364" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="367">
-        <v>1.6248077154159546</v>
-      </c>
-      <c r="G25" s="369" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="372" t="s">
-        <v>75</v>
-      </c>
+      <c r="A25" s="371" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="372"/>
     </row>
     <row r="26">
       <c r="A26" s="375" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" s="377" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C26" s="380">
-        <v>1.4352699518203735</v>
+        <v>1.6031218767166138</v>
       </c>
       <c r="D26" s="382" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E26" s="384" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F26" s="387">
-        <v>1.4456832408905029</v>
+        <v>1.5620499849319458</v>
       </c>
       <c r="G26" s="389" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H26" s="392" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="395" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="397" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C27" s="400">
-        <v>1.3266499042510986</v>
+        <v>1.6124515533447266</v>
       </c>
       <c r="D27" s="402" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E27" s="404" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F27" s="407">
-        <v>1.3304134607315064</v>
+        <v>1.6248077154159546</v>
       </c>
       <c r="G27" s="409" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H27" s="412" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="415" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B28" s="417" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="420">
-        <v>3.2634334564208984</v>
+        <v>1.4352699518203735</v>
       </c>
       <c r="D28" s="422" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" s="424" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F28" s="427">
-        <v>3.1646475791931152</v>
+        <v>1.4456832408905029</v>
       </c>
       <c r="G28" s="429" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H28" s="432" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="436" t="s">
+      <c r="A29" s="435" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="439" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="443">
-        <v>8.0586690902709961</v>
-      </c>
-      <c r="D29" s="446" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="449" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" s="453">
-        <v>7.8742549419403076</v>
-      </c>
-      <c r="G29" s="456" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29" s="460" t="s">
-        <v>86</v>
+      <c r="B29" s="437" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="440">
+        <v>1.3266499042510986</v>
+      </c>
+      <c r="D29" s="442" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="444" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="447">
+        <v>1.3304134607315064</v>
+      </c>
+      <c r="G29" s="449" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" s="452" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
-        <v>87</v>
+      <c r="A30" s="455" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="457" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="460">
+        <v>3.2634334564208984</v>
+      </c>
+      <c r="D30" s="462" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="464" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="467">
+        <v>3.1646475791931152</v>
+      </c>
+      <c r="G30" s="469" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="472" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
-        <v>88</v>
+      <c r="A31" s="476" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="479" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="483">
+        <v>8.0586690902709961</v>
+      </c>
+      <c r="D31" s="486" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="489" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="493">
+        <v>7.8742549419403076</v>
+      </c>
+      <c r="G31" s="496" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="500" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
